--- a/assumption_checking/allsites_atlas_results.xlsx
+++ b/assumption_checking/allsites_atlas_results.xlsx
@@ -158,6 +158,9 @@
     <t xml:space="preserve">Priest BRZ to Lower Ringold</t>
   </si>
   <si>
+    <t xml:space="preserve">Release to Lower Ringold</t>
+  </si>
+  <si>
     <t xml:space="preserve">SPP: CHN ; release: PR</t>
   </si>
   <si>
@@ -201,9 +204,6 @@
   </si>
   <si>
     <t xml:space="preserve">Total:  259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Release to Lower Ringold</t>
   </si>
   <si>
     <t xml:space="preserve">SPP: STH ; release: RI</t>
@@ -956,31 +956,60 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.9167</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.01701</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.9103</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.018685</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9004</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.018538</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.2060121018858</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.813823227427566</v>
+        <v>32</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" t="s">
+        <v>39</v>
+      </c>
+      <c r="I23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0.7352</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.024342</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.7304</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.025926</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.7123</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.024915</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.232056295235327</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.792901485474531</v>
       </c>
     </row>
   </sheetData>
@@ -996,13 +1025,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -1018,68 +1047,68 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -1113,7 +1142,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B12" t="n">
         <v>0.9398</v>
@@ -1464,31 +1493,60 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.9163</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.017072</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.8878</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.022043</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.8531</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.030374</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.76789365712664</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.170692146624465</v>
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0.7289</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.024396</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.6454</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.028488</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.034256</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9.33810092857074</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0000880064079458428</v>
       </c>
     </row>
   </sheetData>
@@ -1529,7 +1587,7 @@
         <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>90</v>
@@ -1537,24 +1595,24 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -1562,7 +1620,7 @@
         <v>91</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
         <v>92</v>
@@ -1573,7 +1631,7 @@
         <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
         <v>94</v>
@@ -1581,7 +1639,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
         <v>95</v>
@@ -1621,7 +1679,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B12" t="n">
         <v>0.8996</v>
